--- a/2026年2月川浪チームクラス図.xlsx
+++ b/2026年2月川浪チームクラス図.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E99E645C-9125-4BB7-9D19-51A8216C9AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C9CF2A-8DF7-4BAF-A91A-19F7121192A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4A5C6957-A10A-4165-9F34-E4D3E143624A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="84">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -58,10 +58,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・シングルトン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・グローバル変数</t>
     <rPh sb="6" eb="8">
       <t>ヘンスウ</t>
@@ -603,6 +599,42 @@
     <rPh sb="8" eb="10">
       <t>カンリ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基底クラス</t>
+    <rPh sb="0" eb="2">
+      <t>キテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シングルトンクラス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・基底クラス</t>
+    <rPh sb="1" eb="3">
+      <t>キテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームマネージャーベース</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーンマネージャが持っている〇〇マネージャーの基底クラス</t>
+    <rPh sb="9" eb="10">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>キテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・シングルトンクラス</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -627,7 +659,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -637,6 +669,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,14 +699,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -686,6 +733,62 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>432144</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>119902</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>577741</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>36900</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="85" name="直線矢印コネクタ 84">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91EF2886-EDDC-7C47-BCF4-9CC9F905F5A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="95" idx="1"/>
+          <a:endCxn id="44" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="4514287" y="7467759"/>
+          <a:ext cx="3547383" cy="1141641"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>624567</xdr:colOff>
       <xdr:row>3</xdr:row>
@@ -788,10 +891,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -828,16 +928,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>595592</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>228199</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>125506</xdr:rowOff>
+      <xdr:rowOff>193542</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>614642</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>211231</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>247249</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>34338</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -852,17 +952,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9440235" y="4779149"/>
+          <a:off x="12474628" y="4847185"/>
           <a:ext cx="2740478" cy="1065439"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -899,16 +996,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>356746</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>669711</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>220436</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>375797</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>235323</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>8404</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>58430</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -923,17 +1020,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12603175" y="4806043"/>
+          <a:off x="15637568" y="4874079"/>
           <a:ext cx="2740479" cy="1062637"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -970,128 +1064,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>191460</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>618926</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>9524</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>634092</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>147917</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AF631A0-797D-A1CD-2213-0C355912E6D0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="2"/>
-          <a:endCxn id="4" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="7675389" y="1968953"/>
-          <a:ext cx="3164060" cy="2832607"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>605117</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>634092</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>125506</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="直線矢印コネクタ 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{542C1AC7-EE74-65E5-9915-5DDA14823A08}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="2"/>
-          <a:endCxn id="5" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="10810474" y="1968953"/>
-          <a:ext cx="28975" cy="2810196"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>634092</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>366272</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>218674</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1104,13 +1086,13 @@
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="2"/>
-          <a:endCxn id="6" idx="0"/>
+          <a:endCxn id="16" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10839449" y="1968953"/>
-          <a:ext cx="3133966" cy="2837090"/>
+        <a:xfrm flipH="1">
+          <a:off x="10824283" y="1968953"/>
+          <a:ext cx="15166" cy="1678721"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1139,11 +1121,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>229960</xdr:colOff>
+      <xdr:colOff>216353</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>140153</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2159566" cy="328423"/>
+      <xdr:rowOff>221795</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2159566" cy="564514"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="14" name="テキスト ボックス 13">
@@ -1157,8 +1139,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9754960" y="2099582"/>
-          <a:ext cx="2159566" cy="328423"/>
+          <a:off x="9741353" y="2181224"/>
+          <a:ext cx="2159566" cy="564514"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1187,8 +1169,16 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>現在のシーンに応じて更新処理</a:t>
+            <a:t>基底クラスのポインタを持ち、</a:t>
           </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>現在のシーンの更新処理を行う</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1196,16 +1186,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>47464</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>360428</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>128308</xdr:rowOff>
+      <xdr:rowOff>196344</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>66514</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>211231</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>379479</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>34338</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1220,7 +1210,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15695678" y="4781951"/>
+          <a:off x="18730071" y="4849987"/>
           <a:ext cx="2740479" cy="1062637"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1397,15 +1387,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>327369</xdr:colOff>
+      <xdr:colOff>422618</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>20571</xdr:rowOff>
+      <xdr:rowOff>34177</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>346420</xdr:colOff>
+      <xdr:colOff>441669</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>106296</xdr:rowOff>
+      <xdr:rowOff>119902</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1420,17 +1410,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048798" y="6388714"/>
+          <a:off x="3144047" y="6402320"/>
           <a:ext cx="2740479" cy="1065439"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -1467,16 +1454,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>185296</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>443831</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>35217</xdr:rowOff>
+      <xdr:rowOff>116860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>204346</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>13606</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>130547</xdr:rowOff>
+      <xdr:rowOff>212190</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1491,17 +1478,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6308510" y="6403360"/>
-          <a:ext cx="2740479" cy="1075044"/>
+          <a:off x="9288474" y="6485003"/>
+          <a:ext cx="2971561" cy="1075044"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -1535,9 +1519,6 @@
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
             <a:t>UI</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr lvl="0" algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
             <a:t>マネージャー</a:t>
@@ -1555,10 +1536,10 @@
       <xdr:rowOff>203427</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>56989</xdr:colOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>369954</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>128308</xdr:rowOff>
+      <xdr:rowOff>196344</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1577,7 +1558,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12209688" y="1428070"/>
-          <a:ext cx="4856230" cy="3353881"/>
+          <a:ext cx="7890623" cy="3421917"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1605,10 +1586,10 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>372994</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>134470</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>291351</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>229720</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1595309" cy="564514"/>
     <xdr:sp macro="" textlink="">
@@ -1624,7 +1605,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13299780" y="2583756"/>
+          <a:off x="12537780" y="1699291"/>
           <a:ext cx="1595309" cy="564514"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1670,16 +1651,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>609838</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>242445</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>55547</xdr:rowOff>
+      <xdr:rowOff>123583</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>628888</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>261495</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>150877</xdr:rowOff>
+      <xdr:rowOff>218913</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1694,17 +1675,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9454481" y="6423690"/>
+          <a:off x="12488874" y="6491726"/>
           <a:ext cx="2740478" cy="1075044"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -1749,16 +1727,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>345219</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>658184</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>15045</xdr:rowOff>
+      <xdr:rowOff>123902</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>364269</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>677233</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>110375</xdr:rowOff>
+      <xdr:rowOff>219232</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1773,17 +1751,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12591648" y="6383188"/>
+          <a:off x="15626041" y="6492045"/>
           <a:ext cx="2740478" cy="1075044"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -1829,7 +1804,7 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>336895</xdr:colOff>
+      <xdr:colOff>432144</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>233642</xdr:rowOff>
     </xdr:from>
@@ -1837,7 +1812,7 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>191460</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>20571</xdr:rowOff>
+      <xdr:rowOff>34177</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1855,8 +1830,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="4419038" y="5866999"/>
-          <a:ext cx="3256351" cy="521715"/>
+          <a:off x="4514287" y="5866999"/>
+          <a:ext cx="3161102" cy="535321"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1890,10 +1865,10 @@
       <xdr:rowOff>233642</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>194821</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>568898</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>35217</xdr:rowOff>
+      <xdr:rowOff>116860</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1912,7 +1887,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7675389" y="5866999"/>
-          <a:ext cx="3361" cy="536361"/>
+          <a:ext cx="3098866" cy="618004"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1940,16 +1915,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>605117</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>211231</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>237724</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>34338</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>619363</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>251970</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>55547</xdr:rowOff>
+      <xdr:rowOff>123583</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1967,7 +1942,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10810474" y="5844588"/>
+          <a:off x="13844867" y="5912624"/>
           <a:ext cx="14246" cy="579102"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -1996,16 +1971,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>354744</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>235323</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>667709</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>58430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>366272</xdr:colOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>679237</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>15045</xdr:rowOff>
+      <xdr:rowOff>123902</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2023,8 +1998,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="13961887" y="5868680"/>
-          <a:ext cx="11528" cy="514508"/>
+          <a:off x="16996280" y="5936716"/>
+          <a:ext cx="11528" cy="555329"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2052,14 +2027,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>588627</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>615841</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>200186</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>607677</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>634892</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>40982</xdr:rowOff>
     </xdr:to>
@@ -2076,7 +2051,386 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1268984" y="8037900"/>
+          <a:off x="4697984" y="8037900"/>
+          <a:ext cx="2740479" cy="1065439"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>ステージマネージャー</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>577741</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>234204</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>596792</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>84525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="95" name="正方形/長方形 94">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1907736-5DC1-46B1-A854-1175E76F4DB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8061670" y="8071918"/>
+          <a:ext cx="2740479" cy="1074964"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>プレイヤー</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>580461</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>83165</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>599512</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>168889</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="96" name="正方形/長方形 95">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F7FDDD0-7E0E-4274-95F9-A68906D8F99A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8064390" y="9635379"/>
+          <a:ext cx="2740479" cy="1065439"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>必殺技</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>604955</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>57311</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>624006</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>152560</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="97" name="正方形/長方形 96">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5E48F7E-3185-4769-90CF-A576954F1420}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4687098" y="9609525"/>
+          <a:ext cx="2740479" cy="1074964"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>ステージ床</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>614481</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>40982</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>625367</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>57311</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="101" name="直線矢印コネクタ 100">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD9075AF-03E4-4CB2-86EF-3F0390628CA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="94" idx="2"/>
+          <a:endCxn id="97" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="6057338" y="9103339"/>
+          <a:ext cx="10886" cy="506186"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>587267</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>84525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>589987</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>83165</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="108" name="直線矢印コネクタ 107">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0E435D8-C66C-4771-BC54-604A20E635FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="95" idx="2"/>
+          <a:endCxn id="96" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9431910" y="9146882"/>
+          <a:ext cx="2720" cy="488497"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>347942</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>68995</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>366993</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>154720</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="112" name="正方形/長方形 111">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96D89708-81E2-4783-BFE1-3F178CEF2FCC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3069371" y="4722638"/>
           <a:ext cx="2740479" cy="1065439"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2114,9 +2468,8 @@
           <a:pPr lvl="0" algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-            <a:t>ステージマネージャー</a:t>
+            <a:t>フェードマネージャー</a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2125,508 +2478,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>550527</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>243729</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>569578</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>84525</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="95" name="正方形/長方形 94">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1907736-5DC1-46B1-A854-1175E76F4DB3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4632670" y="8081443"/>
-          <a:ext cx="2740479" cy="1065439"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0" algn="ctr"/>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-        </a:p>
-        <a:p>
-          <a:pPr lvl="0" algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-            <a:t>プレイヤー</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>553247</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>83165</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>572298</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>168889</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="96" name="正方形/長方形 95">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F7FDDD0-7E0E-4274-95F9-A68906D8F99A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4635390" y="9635379"/>
-          <a:ext cx="2740479" cy="1065439"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0" algn="ctr"/>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-        </a:p>
-        <a:p>
-          <a:pPr lvl="0" algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-            <a:t>必殺技</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>577741</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>57311</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>596791</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>152560</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="97" name="正方形/長方形 96">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5E48F7E-3185-4769-90CF-A576954F1420}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1258098" y="9609525"/>
-          <a:ext cx="2740479" cy="1074964"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0" algn="ctr"/>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-        </a:p>
-        <a:p>
-          <a:pPr lvl="0" algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-            <a:t>ステージ床</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>598153</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>106296</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>336895</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>200186</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="98" name="直線矢印コネクタ 97">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{286F5527-9FF8-426B-93DE-0F87110C8ABC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="44" idx="2"/>
-          <a:endCxn id="94" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="2639224" y="7454153"/>
-          <a:ext cx="1779814" cy="583747"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>587267</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>40982</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>598153</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>57311</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="101" name="直線矢印コネクタ 100">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD9075AF-03E4-4CB2-86EF-3F0390628CA2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="94" idx="2"/>
-          <a:endCxn id="97" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="2628338" y="9103339"/>
-          <a:ext cx="10886" cy="506186"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>336895</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>106296</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>560053</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>234204</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="104" name="直線矢印コネクタ 103">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6811724A-0D1B-41A8-A4B8-3546AA13B8B0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="44" idx="2"/>
-          <a:endCxn id="95" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4419038" y="7454153"/>
-          <a:ext cx="1583872" cy="617765"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>560053</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>84525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>562773</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>83165</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="108" name="直線矢印コネクタ 107">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0E435D8-C66C-4771-BC54-604A20E635FE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="95" idx="2"/>
-          <a:endCxn id="96" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6002910" y="9146882"/>
-          <a:ext cx="2720" cy="488497"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>456799</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>123424</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>475850</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>209149</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="112" name="正方形/長方形 111">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96D89708-81E2-4783-BFE1-3F178CEF2FCC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3178228" y="3552424"/>
-          <a:ext cx="2740479" cy="1065439"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0" algn="ctr"/>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-        </a:p>
-        <a:p>
-          <a:pPr lvl="0" algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-            <a:t>フェードマネージャー</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>466325</xdr:colOff>
+      <xdr:colOff>357468</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>203427</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>624567</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>123424</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>68995</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2644,8 +2504,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="4548468" y="1428070"/>
-          <a:ext cx="4920742" cy="2124354"/>
+          <a:off x="4439611" y="1428070"/>
+          <a:ext cx="5029599" cy="3294568"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2802,16 +2662,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>335532</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>232844</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>430783</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>110380</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>354583</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>73640</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>449833</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>196105</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2826,7 +2686,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7819461" y="8070558"/>
+          <a:off x="11316497" y="8682880"/>
           <a:ext cx="2740479" cy="1065439"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2868,16 +2728,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>338253</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>221958</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>433503</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>99494</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>357303</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>62754</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>452554</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>185219</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2892,7 +2752,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10543610" y="8059672"/>
+          <a:off x="14040646" y="8671994"/>
           <a:ext cx="2740479" cy="1065439"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2934,16 +2794,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>327367</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>224680</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>422618</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>102216</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>346418</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>65476</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>441668</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>187941</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2958,7 +2818,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13254153" y="8062394"/>
+          <a:off x="16751189" y="8674716"/>
           <a:ext cx="2740479" cy="1065439"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3000,16 +2860,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>194821</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>568898</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>130547</xdr:rowOff>
+      <xdr:rowOff>212190</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>347779</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>221958</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>443029</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>99494</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3027,8 +2887,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7678750" y="7478404"/>
-          <a:ext cx="4235100" cy="581268"/>
+          <a:off x="10774255" y="7560047"/>
+          <a:ext cx="4636631" cy="1111947"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3056,16 +2916,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>619363</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>251970</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>150877</xdr:rowOff>
+      <xdr:rowOff>218913</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>347779</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>221958</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>443029</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>99494</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3083,8 +2943,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10824720" y="7498734"/>
-          <a:ext cx="1089130" cy="560938"/>
+          <a:off x="13859113" y="7566770"/>
+          <a:ext cx="1551773" cy="1105224"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3112,16 +2972,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>347779</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>443029</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>110375</xdr:rowOff>
+      <xdr:rowOff>219232</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>354744</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>221958</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>667709</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>99494</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3139,8 +2999,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="11913850" y="7458232"/>
-          <a:ext cx="2048037" cy="601440"/>
+          <a:off x="15410886" y="7567089"/>
+          <a:ext cx="1585394" cy="1104905"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3169,15 +3029,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>554208</xdr:colOff>
+      <xdr:colOff>581423</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>134150</xdr:rowOff>
+      <xdr:rowOff>161365</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>573258</xdr:colOff>
+      <xdr:colOff>600473</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>217073</xdr:rowOff>
+      <xdr:rowOff>244288</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3192,7 +3052,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20964922" y="868936"/>
+          <a:off x="20992137" y="896151"/>
           <a:ext cx="2740479" cy="1062637"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3306,13 +3166,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>563733</xdr:colOff>
+      <xdr:colOff>584542</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>217073</xdr:rowOff>
+      <xdr:rowOff>234763</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>584542</xdr:colOff>
+      <xdr:colOff>590948</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>241007</xdr:rowOff>
     </xdr:to>
@@ -3331,9 +3191,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="22335162" y="1931573"/>
-          <a:ext cx="20809" cy="758720"/>
+        <a:xfrm flipH="1">
+          <a:off x="22355971" y="1949263"/>
+          <a:ext cx="6406" cy="741030"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3411,6 +3271,704 @@
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
             <a:t>出したい奴が出す</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>476251</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>218674</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>81243</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>59470</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="正方形/長方形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A826EB1-E594-4CF8-98FC-818AFD546BE1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9320894" y="3647674"/>
+          <a:ext cx="3006778" cy="1065439"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>ゲームマネージャーベース</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>191460</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>16608</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>476251</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>147917</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="直線矢印コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A64C5070-544E-C37E-33D5-B592BA5E2630}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="1"/>
+          <a:endCxn id="4" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="7675389" y="4180394"/>
+          <a:ext cx="1645505" cy="621166"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>81243</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>16608</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>237724</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>193542</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="直線矢印コネクタ 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC683641-D1EB-4E07-95EA-F08994687EBC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="3"/>
+          <a:endCxn id="5" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12327672" y="4180394"/>
+          <a:ext cx="1517195" cy="666791"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>81243</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>16608</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>679237</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>220436</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="26" name="直線矢印コネクタ 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FA7F4C7-53E7-4AC3-84B5-148DB522638A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="3"/>
+          <a:endCxn id="6" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12327672" y="4180394"/>
+          <a:ext cx="4680136" cy="693685"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>571498</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>163285</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="466794" cy="328423"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="テキスト ボックス 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A84C382-CEB7-25AF-5D7F-617237F35FBD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8735784" y="4327071"/>
+          <a:ext cx="466794" cy="328423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>継承</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>326572</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2300630" cy="328423"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="テキスト ボックス 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0765929-0D4C-2E61-EF6D-8B0BBE341BB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6449786" y="2340429"/>
+          <a:ext cx="2300630" cy="328423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>シーン切り替え時にフェード処理</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>625367</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>233642</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>191460</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>200186</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="73" name="直線矢印コネクタ 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2724A9F6-9264-4E5C-87E7-1B290505613B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="2"/>
+          <a:endCxn id="94" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="6068224" y="5866999"/>
+          <a:ext cx="1607165" cy="2170901"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>191460</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>233642</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>587267</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>234204</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="78" name="直線矢印コネクタ 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1B72F95-3516-4563-99AA-7B7A40E156C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="2"/>
+          <a:endCxn id="95" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7675389" y="5866999"/>
+          <a:ext cx="1756521" cy="2204919"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>432144</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>119902</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>615841</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>243049</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="87" name="直線矢印コネクタ 86">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EB12FE3-D268-469F-B284-ECA9A6262845}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="94" idx="1"/>
+          <a:endCxn id="44" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="4514287" y="7467759"/>
+          <a:ext cx="183697" cy="1102861"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>231322</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>231321</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2582758" cy="328423"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="92" name="テキスト ボックス 91">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A20C7C29-4BA9-D629-42B4-A27237E346A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2272393" y="7824107"/>
+          <a:ext cx="2582758" cy="328423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ステージ床の当たり判定の配列を渡す</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>394608</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>68035</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2723823" cy="328423"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="93" name="テキスト ボックス 92">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BCC3674-2AEA-D8ED-8521-09F7181B4814}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5157108" y="7660821"/>
+          <a:ext cx="2723823" cy="328423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>プレイヤーと必殺技の当たり判定を渡す</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>179612</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>125185</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="466794" cy="328423"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="107" name="テキスト ボックス 106">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40A34754-BF85-4E4B-B68E-29198987AF6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12426041" y="4288971"/>
+          <a:ext cx="466794" cy="328423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>継承</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3737,11 +4295,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FB87732-1241-49E3-84A9-A00C3F31C3EC}">
-  <dimension ref="A2:F35"/>
+  <dimension ref="A2:F37"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="31.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="62.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="56.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="112.625" bestFit="1" customWidth="1"/>
@@ -3752,19 +4310,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -3772,13 +4330,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
@@ -3786,269 +4344,272 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" t="s">
-        <v>35</v>
+        <v>70</v>
+      </c>
+      <c r="E14" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" t="s">
-        <v>72</v>
+        <v>77</v>
+      </c>
+      <c r="E16" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B17" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" t="s">
-        <v>73</v>
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" t="s">
-        <v>74</v>
+    <row r="18" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" t="s">
-        <v>56</v>
+    <row r="20" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" t="s">
-        <v>55</v>
+        <v>41</v>
+      </c>
+      <c r="F22" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B23" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>67</v>
+      </c>
+      <c r="D23" t="s">
+        <v>33</v>
       </c>
       <c r="E23" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="F23" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B24" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B26" t="s">
-        <v>60</v>
+        <v>39</v>
+      </c>
+      <c r="C26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B27" t="s">
-        <v>58</v>
+    <row r="27" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B28" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B29" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
@@ -4058,22 +4619,32 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B32" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B34" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B35" t="s">
-        <v>67</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B37" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4084,11 +4655,48 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D86A6C4-08D9-47DA-8EAD-E993876FE141}">
-  <dimension ref="B2"/>
+  <dimension ref="B2:E7"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/2026年2月川浪チームクラス図.xlsx
+++ b/2026年2月川浪チームクラス図.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opencampus\Downloads\Fall3-main\Fall3-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C9CF2A-8DF7-4BAF-A91A-19F7121192A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A8FDC4-0188-484E-A031-91E2C195EBE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4A5C6957-A10A-4165-9F34-E4D3E143624A}"/>
   </bookViews>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1186,16 +1189,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>360428</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>196344</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>305999</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>101094</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>379479</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>34338</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>325050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>184016</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1210,7 +1213,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18730071" y="4849987"/>
+          <a:off x="13913142" y="2795308"/>
           <a:ext cx="2740479" cy="1062637"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1536,10 +1539,10 @@
       <xdr:rowOff>203427</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>369954</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>196344</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>315525</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>101094</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1558,7 +1561,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12209688" y="1428070"/>
-          <a:ext cx="7890623" cy="3421917"/>
+          <a:ext cx="3073694" cy="1367238"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2406,133 +2409,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>347942</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>68995</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>366993</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>154720</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="112" name="正方形/長方形 111">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96D89708-81E2-4783-BFE1-3F178CEF2FCC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3069371" y="4722638"/>
-          <a:ext cx="2740479" cy="1065439"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0" algn="ctr"/>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-        </a:p>
-        <a:p>
-          <a:pPr lvl="0" algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-            <a:t>フェードマネージャー</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>357468</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>203427</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>624567</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>68995</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="113" name="直線矢印コネクタ 112">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60D477C0-47AA-41B0-B486-CE02C3105D69}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="1"/>
-          <a:endCxn id="112" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="4439611" y="1428070"/>
-          <a:ext cx="5029599" cy="3294568"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>26</xdr:col>
       <xdr:colOff>156879</xdr:colOff>
       <xdr:row>3</xdr:row>
@@ -3569,64 +3445,6 @@
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
             <a:t>継承</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>326572</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>136072</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2300630" cy="328423"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="テキスト ボックス 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0765929-0D4C-2E61-EF6D-8B0BBE341BB6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6449786" y="2340429"/>
-          <a:ext cx="2300630" cy="328423"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>シーン切り替え時にフェード処理</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>

--- a/2026年2月川浪チームクラス図.xlsx
+++ b/2026年2月川浪チームクラス図.xlsx
@@ -5,16 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opencampus\Downloads\Fall3-main\Fall3-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opencampus\Documents\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A8FDC4-0188-484E-A031-91E2C195EBE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A68A403-B687-413A-830A-426A23B74BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4A5C6957-A10A-4165-9F34-E4D3E143624A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{4A5C6957-A10A-4165-9F34-E4D3E143624A}"/>
   </bookViews>
   <sheets>
     <sheet name="クラス一覧" sheetId="1" r:id="rId1"/>
     <sheet name="クラス図" sheetId="2" r:id="rId2"/>
+    <sheet name="インプットマネージャー" sheetId="5" r:id="rId3"/>
+    <sheet name="サウンドマネージャー" sheetId="6" r:id="rId4"/>
+    <sheet name="エフェクトマネージャー" sheetId="7" r:id="rId5"/>
+    <sheet name="ゲームマネージャーベース" sheetId="4" r:id="rId6"/>
+    <sheet name="シーンマネージャー" sheetId="3" r:id="rId7"/>
+    <sheet name="カメラマネージャー" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,8 +34,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -40,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="117">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -638,6 +642,375 @@
   </si>
   <si>
     <t>・シングルトンクラス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラス名</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>概要</t>
+    <rPh sb="0" eb="2">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーンの切り替えを管理する。</t>
+    <rPh sb="4" eb="5">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラクラス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームマネージャーベースのポインタ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーンの切り替え時にこのポインタの中身を入れ替える。</t>
+    <rPh sb="4" eb="5">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ナカミ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーン全体の動きを制御するクラスの基底クラス。</t>
+    <rPh sb="3" eb="5">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーンマネージャーはこの関数でシーンが終わったかどうか見て、シーン遷移をする</t>
+    <rPh sb="12" eb="14">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Update()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在のシーンによってカメラの位置を変え、疑似シーン遷移的な感じにする</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ギジ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自身と自身が持っているクラスの更新処理を行う</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>コウシンショリ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コントローラーやキーボードの入力を取得し、それを開示する</t>
+    <rPh sb="14" eb="16">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カイジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何らかの形で入力を保存しておく</t>
+    <rPh sb="0" eb="1">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自身が取得した入力を渡す</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ワタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bool シーンが終わったかどうか</t>
+    <rPh sb="9" eb="10">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーンが終わったらtrueになる</t>
+    <rPh sb="4" eb="5">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音を鳴らす()</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音を鳴らす</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音を止める()</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音を止める</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いろんな場所から命令を受け取り音を鳴らしたり止めたりする</t>
+    <rPh sb="4" eb="6">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>メイレイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いろんな場所から命令を受け取りエフェクトを出す</t>
+    <rPh sb="4" eb="6">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>メイレイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロードした音を保存しておく</t>
+    <rPh sb="5" eb="6">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロードしたエフェクトを保存しておく</t>
+    <rPh sb="11" eb="13">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エフェクトを再生する</t>
+    <rPh sb="6" eb="8">
+      <t>サイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エフェクト再生(位置、エフェクトの種類)</t>
+    <rPh sb="5" eb="7">
+      <t>サイセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>get入力(欲しい入力の種類)</t>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ホ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>getシーンが終わったかどうか()</t>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラの管理をする</t>
+    <rPh sb="4" eb="6">
+      <t>カンリ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1190,15 +1563,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>305999</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>101094</xdr:rowOff>
+      <xdr:colOff>33856</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>237165</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>325050</xdr:colOff>
+      <xdr:colOff>52907</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>184016</xdr:rowOff>
+      <xdr:rowOff>75159</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1213,7 +1586,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13913142" y="2795308"/>
+          <a:off x="13640999" y="2686451"/>
           <a:ext cx="2740479" cy="1062637"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1251,7 +1624,7 @@
           <a:pPr lvl="0" algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-            <a:t>カメラ</a:t>
+            <a:t>カメラマネージャー</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1540,9 +1913,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>315525</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>101094</xdr:rowOff>
+      <xdr:colOff>43382</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>237165</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1561,7 +1934,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12209688" y="1428070"/>
-          <a:ext cx="3073694" cy="1367238"/>
+          <a:ext cx="2801551" cy="1258381"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3793,6 +4166,201 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>586468</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>61231</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2864887" cy="800604"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="テキスト ボックス 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D78283F-2A3D-4F26-8B51-C2769B132EA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9431111" y="4714874"/>
+          <a:ext cx="2864887" cy="800604"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>シーンが終わったかどうかを持っており、</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>それを見てシーンマネージャーが</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>シーン遷移をする</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>196737</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>216514</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>215788</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>57310</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="正方形/長方形 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{983FA59B-21E3-42DB-AE10-EFAB346DD7F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17205666" y="2665800"/>
+          <a:ext cx="2740479" cy="1065439"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>カメラ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>52907</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>14449</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>196737</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>33699</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="56" name="直線矢印コネクタ 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D12B77E-E0A6-4387-BD88-F952BD2D29F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="15" idx="3"/>
+          <a:endCxn id="55" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="16381478" y="3198520"/>
+          <a:ext cx="824188" cy="19250"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4521,4 +5089,376 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2460D3FB-76ED-4260-9C5D-8BE6761BF117}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{088CDA82-8AD8-434D-B4C2-7B988A15604E}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AC06B73-86F7-4C09-AF6B-D4BF4F6B976C}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="39.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DC90C96-0A10-44ED-A2F6-7AFD9C29B747}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="35.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D89FAE-06BF-4E6F-A776-ADA5B50E52C1}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="35.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B2D662D-8746-403E-9448-1C220BEBC9B5}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="35.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/2026年2月川浪チームクラス図.xlsx
+++ b/2026年2月川浪チームクラス図.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opencampus\Documents\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A68A403-B687-413A-830A-426A23B74BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6A62A9-1063-4A9F-A6A0-FEBE0FD53FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{4A5C6957-A10A-4165-9F34-E4D3E143624A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="864" activeTab="11" xr2:uid="{4A5C6957-A10A-4165-9F34-E4D3E143624A}"/>
   </bookViews>
   <sheets>
     <sheet name="クラス一覧" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,14 @@
     <sheet name="インプットマネージャー" sheetId="5" r:id="rId3"/>
     <sheet name="サウンドマネージャー" sheetId="6" r:id="rId4"/>
     <sheet name="エフェクトマネージャー" sheetId="7" r:id="rId5"/>
-    <sheet name="ゲームマネージャーベース" sheetId="4" r:id="rId6"/>
+    <sheet name="エフェクト" sheetId="10" r:id="rId6"/>
     <sheet name="シーンマネージャー" sheetId="3" r:id="rId7"/>
     <sheet name="カメラマネージャー" sheetId="8" r:id="rId8"/>
+    <sheet name="カメラ" sheetId="9" r:id="rId9"/>
+    <sheet name="ゲームマネージャーベース" sheetId="4" r:id="rId10"/>
+    <sheet name="タイトルマネージャー" sheetId="11" r:id="rId11"/>
+    <sheet name="タイトルUIマネージャー" sheetId="13" r:id="rId12"/>
+    <sheet name="リザルトマネージャー" sheetId="12" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,15 +41,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="139">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -702,10 +704,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ゲームマネージャー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>シーン全体の動きを制御するクラスの基底クラス。</t>
     <rPh sb="3" eb="5">
       <t>ゼンタイ</t>
@@ -852,23 +850,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>音</t>
-    <rPh sb="0" eb="1">
-      <t>オト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音を鳴らす()</t>
-    <rPh sb="0" eb="1">
-      <t>オト</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>音を鳴らす</t>
     <rPh sb="0" eb="1">
       <t>オト</t>
@@ -879,16 +860,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>音を止める()</t>
-    <rPh sb="0" eb="1">
-      <t>オト</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>音を止める</t>
     <rPh sb="0" eb="1">
       <t>オト</t>
@@ -1009,6 +980,200 @@
   <si>
     <t>カメラの管理をする</t>
     <rPh sb="4" eb="6">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>命名規則</t>
+    <rPh sb="0" eb="4">
+      <t>メイメイキソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>定数</t>
+    <rPh sb="0" eb="2">
+      <t>テイスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローカル変数</t>
+    <rPh sb="4" eb="6">
+      <t>ヘンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>頭にkをつける</t>
+    <rPh sb="0" eb="1">
+      <t>アタマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最初は小文字、次の単語から頭文字大文字</t>
+    <rPh sb="0" eb="2">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>コモジ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タンゴ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>カシラモジ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>オオモジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>頭に_をつける</t>
+    <rPh sb="0" eb="1">
+      <t>アタマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kPlayerMoveSpeed</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>playerVelocity</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>_playerPos</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポインタ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>頭にpをつける</t>
+    <rPh sb="0" eb="1">
+      <t>アタマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pPlayer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エフェクト[]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音[]</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音を鳴らす(音の種類)</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音を止める(音の種類)</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>位置</t>
+    <rPh sb="0" eb="2">
+      <t>イチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>向き</t>
+    <rPh sb="0" eb="1">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エフェクト本体</t>
+    <rPh sb="5" eb="7">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラ本体</t>
+    <rPh sb="3" eb="5">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルシーンを管理するクラス</t>
+    <rPh sb="8" eb="10">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームマネージャーベースを継承する</t>
+    <rPh sb="13" eb="15">
+      <t>ケイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI制御のための変数(indexとか)</t>
+    <rPh sb="2" eb="4">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヘンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルトシーンを管理するクラス</t>
+    <rPh sb="8" eb="10">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルシーンのUIを管理するクラス</t>
+    <rPh sb="11" eb="13">
       <t>カンリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -4681,356 +4846,647 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FB87732-1241-49E3-84A9-A00C3F31C3EC}">
-  <dimension ref="A2:F37"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="31.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="58.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="62.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="56.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="112.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" t="s">
-        <v>27</v>
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" t="s">
-        <v>72</v>
+        <v>45</v>
+      </c>
+      <c r="E12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" t="s">
-        <v>73</v>
+        <v>49</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" t="s">
-        <v>55</v>
+        <v>40</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" t="s">
-        <v>55</v>
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B17" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="1" t="s">
-        <v>80</v>
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
+      </c>
+      <c r="E19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
+        <v>77</v>
+      </c>
+      <c r="E21" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" t="s">
-        <v>51</v>
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B24" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" t="s">
-        <v>53</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B26" t="s">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="1" t="s">
-        <v>4</v>
+        <v>50</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B28" t="s">
-        <v>59</v>
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" t="s">
+        <v>56</v>
+      </c>
+      <c r="F28" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B29" t="s">
-        <v>57</v>
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B30" t="s">
-        <v>61</v>
+        <v>13</v>
+      </c>
+      <c r="C30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B31" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B32" t="s">
-        <v>62</v>
+        <v>39</v>
+      </c>
+      <c r="C31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B39" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B40" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B41" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B42" t="s">
         <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DC90C96-0A10-44ED-A2F6-7AFD9C29B747}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="35.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0FF8188-DC9C-42B9-97AC-AEB9F9C087AF}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C034DE-460C-420D-883F-E36AE2A1B617}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{088DB3FB-82A4-4655-95F0-46DFF6829169}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5116,7 +5572,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -5126,10 +5582,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -5139,10 +5595,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -5176,7 +5632,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -5186,10 +5642,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -5199,18 +5655,18 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -5244,7 +5700,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -5254,10 +5710,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -5267,10 +5723,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -5280,16 +5736,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DC90C96-0A10-44ED-A2F6-7AFD9C29B747}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AC46883-0340-4F21-BBA9-C16EDD64DFF8}">
   <sheetPr>
-    <tabColor theme="4" tint="0.79998168889431442"/>
+    <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="35.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -5302,10 +5757,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -5315,23 +5770,12 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" t="s">
-        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -5377,10 +5821,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
@@ -5398,10 +5842,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -5433,10 +5877,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -5449,7 +5893,60 @@
         <v>87</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7007ECF9-468F-433B-ACE1-3A9ABEA24AEC}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="2" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">

--- a/2026年2月川浪チームクラス図.xlsx
+++ b/2026年2月川浪チームクラス図.xlsx
@@ -8,24 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6A62A9-1063-4A9F-A6A0-FEBE0FD53FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C311E59-6354-43FE-8033-92568EF37F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="864" activeTab="11" xr2:uid="{4A5C6957-A10A-4165-9F34-E4D3E143624A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="864" activeTab="1" xr2:uid="{4A5C6957-A10A-4165-9F34-E4D3E143624A}"/>
   </bookViews>
   <sheets>
     <sheet name="クラス一覧" sheetId="1" r:id="rId1"/>
     <sheet name="クラス図" sheetId="2" r:id="rId2"/>
-    <sheet name="インプットマネージャー" sheetId="5" r:id="rId3"/>
-    <sheet name="サウンドマネージャー" sheetId="6" r:id="rId4"/>
-    <sheet name="エフェクトマネージャー" sheetId="7" r:id="rId5"/>
-    <sheet name="エフェクト" sheetId="10" r:id="rId6"/>
-    <sheet name="シーンマネージャー" sheetId="3" r:id="rId7"/>
-    <sheet name="カメラマネージャー" sheetId="8" r:id="rId8"/>
-    <sheet name="カメラ" sheetId="9" r:id="rId9"/>
-    <sheet name="ゲームマネージャーベース" sheetId="4" r:id="rId10"/>
-    <sheet name="タイトルマネージャー" sheetId="11" r:id="rId11"/>
-    <sheet name="タイトルUIマネージャー" sheetId="13" r:id="rId12"/>
-    <sheet name="リザルトマネージャー" sheetId="12" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="97">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -647,344 +636,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>クラス名</t>
-    <rPh sb="3" eb="4">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>概要</t>
-    <rPh sb="0" eb="2">
-      <t>ガイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>シーンの切り替えを管理する。</t>
-    <rPh sb="4" eb="5">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カメラクラス</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゲームマネージャーベースのポインタ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>シーンの切り替え時にこのポインタの中身を入れ替える。</t>
-    <rPh sb="4" eb="5">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ナカミ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>シーン全体の動きを制御するクラスの基底クラス。</t>
-    <rPh sb="3" eb="5">
-      <t>ゼンタイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ウゴ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>セイギョ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>キテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>シーンマネージャーはこの関数でシーンが終わったかどうか見て、シーン遷移をする</t>
-    <rPh sb="12" eb="14">
-      <t>カンスウ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Update()</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>現在のシーンによってカメラの位置を変え、疑似シーン遷移的な感じにする</t>
-    <rPh sb="0" eb="2">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ギジ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>センイ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>カン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>自身と自身が持っているクラスの更新処理を行う</t>
-    <rPh sb="0" eb="2">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>モ</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>コウシンショリ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>オコナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コントローラーやキーボードの入力を取得し、それを開示する</t>
-    <rPh sb="14" eb="16">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>カイジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>何らかの形で入力を保存しておく</t>
-    <rPh sb="0" eb="1">
-      <t>ナン</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>カタチ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ホゾン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>入力</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>自身が取得した入力を渡す</t>
-    <rPh sb="0" eb="2">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ワタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>bool シーンが終わったかどうか</t>
-    <rPh sb="9" eb="10">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>シーンが終わったらtrueになる</t>
-    <rPh sb="4" eb="5">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音を鳴らす</t>
-    <rPh sb="0" eb="1">
-      <t>オト</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音を止める</t>
-    <rPh sb="0" eb="1">
-      <t>オト</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>いろんな場所から命令を受け取り音を鳴らしたり止めたりする</t>
-    <rPh sb="4" eb="6">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>メイレイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>オト</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>いろんな場所から命令を受け取りエフェクトを出す</t>
-    <rPh sb="4" eb="6">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>メイレイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ロードした音を保存しておく</t>
-    <rPh sb="5" eb="6">
-      <t>オト</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ホゾン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ロードしたエフェクトを保存しておく</t>
-    <rPh sb="11" eb="13">
-      <t>ホゾン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エフェクトを再生する</t>
-    <rPh sb="6" eb="8">
-      <t>サイセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エフェクト再生(位置、エフェクトの種類)</t>
-    <rPh sb="5" eb="7">
-      <t>サイセイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>シュルイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>get入力(欲しい入力の種類)</t>
-    <rPh sb="3" eb="5">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ホ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>シュルイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>getシーンが終わったかどうか()</t>
-    <rPh sb="7" eb="8">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カメラマネージャー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カメラの管理をする</t>
-    <rPh sb="4" eb="6">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>命名規則</t>
     <rPh sb="0" eb="4">
       <t>メイメイキソク</t>
@@ -1073,109 +724,6 @@
   </si>
   <si>
     <t>pPlayer</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エフェクト[]</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音[]</t>
-    <rPh sb="0" eb="1">
-      <t>オト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音を鳴らす(音の種類)</t>
-    <rPh sb="0" eb="1">
-      <t>オト</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>オト</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>シュルイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音を止める(音の種類)</t>
-    <rPh sb="0" eb="1">
-      <t>オト</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>位置</t>
-    <rPh sb="0" eb="2">
-      <t>イチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>向き</t>
-    <rPh sb="0" eb="1">
-      <t>ム</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エフェクト本体</t>
-    <rPh sb="5" eb="7">
-      <t>ホンタイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カメラ本体</t>
-    <rPh sb="3" eb="5">
-      <t>ホンタイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タイトルシーンを管理するクラス</t>
-    <rPh sb="8" eb="10">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゲームマネージャーベースを継承する</t>
-    <rPh sb="13" eb="15">
-      <t>ケイショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>UI制御のための変数(indexとか)</t>
-    <rPh sb="2" eb="4">
-      <t>セイギョ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ヘンスウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>リザルトシーンを管理するクラス</t>
-    <rPh sb="8" eb="10">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タイトルシーンのUIを管理するクラス</t>
-    <rPh sb="11" eb="13">
-      <t>カンリ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4859,32 +4407,32 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
@@ -4892,21 +4440,21 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -5249,244 +4797,6 @@
     <row r="42" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B42" t="s">
         <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DC90C96-0A10-44ED-A2F6-7AFD9C29B747}">
-  <sheetPr>
-    <tabColor theme="4" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="35.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0FF8188-DC9C-42B9-97AC-AEB9F9C087AF}">
-  <sheetPr>
-    <tabColor theme="0"/>
-  </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="30.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C034DE-460C-420D-883F-E36AE2A1B617}">
-  <sheetPr>
-    <tabColor theme="0"/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="30.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{088DB3FB-82A4-4655-95F0-46DFF6829169}">
-  <sheetPr>
-    <tabColor theme="0"/>
-  </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="30.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5545,417 +4855,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2460D3FB-76ED-4260-9C5D-8BE6761BF117}">
-  <sheetPr>
-    <tabColor theme="5" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{088CDA82-8AD8-434D-B4C2-7B988A15604E}">
-  <sheetPr>
-    <tabColor theme="5" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>128</v>
-      </c>
-      <c r="B9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AC06B73-86F7-4C09-AF6B-D4BF4F6B976C}">
-  <sheetPr>
-    <tabColor theme="5" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="39.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" t="s">
-        <v>107</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AC46883-0340-4F21-BBA9-C16EDD64DFF8}">
-  <sheetPr>
-    <tabColor theme="0"/>
-  </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D89FAE-06BF-4E6F-A776-ADA5B50E52C1}">
-  <sheetPr>
-    <tabColor theme="5" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="35.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B2D662D-8746-403E-9448-1C220BEBC9B5}">
-  <sheetPr>
-    <tabColor theme="5" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="35.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7007ECF9-468F-433B-ACE1-3A9ABEA24AEC}">
-  <sheetPr>
-    <tabColor theme="0"/>
-  </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="2" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>